--- a/ZonasEscolares/excels/LIMA-LIMA-LIMA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LIMA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14266,7 +14266,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15514,7 +15514,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15982,7 +15982,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16970,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17074,7 +17074,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17386,7 +17386,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17490,7 +17490,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18010,7 +18010,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18166,7 +18166,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18270,7 +18270,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18582,7 +18582,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18790,7 +18790,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18842,7 +18842,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19050,7 +19050,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19102,7 +19102,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19154,7 +19154,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19310,7 +19310,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19466,7 +19466,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19674,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19726,7 +19726,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19778,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19934,7 +19934,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20090,7 +20090,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20402,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20506,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20558,7 +20558,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20714,7 +20714,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20766,7 +20766,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20922,7 +20922,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -20974,7 +20974,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21130,7 +21130,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21286,7 +21286,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21338,7 +21338,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21598,7 +21598,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21702,7 +21702,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21754,7 +21754,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21858,7 +21858,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21910,7 +21910,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22222,7 +22222,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22326,7 +22326,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22378,7 +22378,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22586,7 +22586,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22690,7 +22690,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22794,7 +22794,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22898,7 +22898,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23002,7 +23002,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23054,7 +23054,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23106,7 +23106,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23158,7 +23158,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23314,7 +23314,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23522,7 +23522,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23574,7 +23574,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23730,7 +23730,7 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23782,7 +23782,7 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23886,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23938,7 +23938,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24094,7 +24094,7 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24146,7 +24146,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24250,7 +24250,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24302,7 +24302,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24354,7 +24354,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24406,7 +24406,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24458,7 +24458,7 @@
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24510,7 +24510,7 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24562,7 +24562,7 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24666,7 +24666,7 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24718,7 +24718,7 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24770,7 +24770,7 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24822,7 +24822,7 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24926,7 +24926,7 @@
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25030,7 +25030,7 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25082,7 +25082,7 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25134,7 +25134,7 @@
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25290,7 +25290,7 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25342,7 +25342,7 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25394,7 +25394,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25446,7 +25446,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25550,7 +25550,7 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25602,7 +25602,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25706,7 +25706,7 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25758,7 +25758,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25810,7 +25810,7 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -25966,7 +25966,7 @@
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -26018,7 +26018,7 @@
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26122,7 +26122,7 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26174,7 +26174,7 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26226,7 +26226,7 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26278,7 +26278,7 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26382,7 +26382,7 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26434,7 +26434,7 @@
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26538,7 +26538,7 @@
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26590,7 +26590,7 @@
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26746,7 +26746,7 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26798,7 +26798,7 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26850,7 +26850,7 @@
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26902,7 +26902,7 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27006,7 +27006,7 @@
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27058,7 +27058,7 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27162,7 +27162,7 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27214,7 +27214,7 @@
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27266,7 +27266,7 @@
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27318,7 +27318,7 @@
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27370,7 +27370,7 @@
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27422,7 +27422,7 @@
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27526,7 +27526,7 @@
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27578,7 +27578,7 @@
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27630,7 +27630,7 @@
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27838,7 +27838,7 @@
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27890,7 +27890,7 @@
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -27994,7 +27994,7 @@
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28046,7 +28046,7 @@
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28098,7 +28098,7 @@
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28150,7 +28150,7 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28410,7 +28410,7 @@
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28462,7 +28462,7 @@
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28514,7 +28514,7 @@
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28566,7 +28566,7 @@
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28618,7 +28618,7 @@
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28670,7 +28670,7 @@
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28722,7 +28722,7 @@
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28774,7 +28774,7 @@
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28878,7 +28878,7 @@
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28930,7 +28930,7 @@
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29034,7 +29034,7 @@
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29086,7 +29086,7 @@
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29190,7 +29190,7 @@
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29242,7 +29242,7 @@
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29346,7 +29346,7 @@
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29398,7 +29398,7 @@
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29450,7 +29450,7 @@
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29554,7 +29554,7 @@
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29710,7 +29710,7 @@
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29762,7 +29762,7 @@
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29814,7 +29814,7 @@
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29918,7 +29918,7 @@
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29970,7 +29970,7 @@
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30022,7 +30022,7 @@
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30126,7 +30126,7 @@
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30282,7 +30282,7 @@
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30334,7 +30334,7 @@
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30386,7 +30386,7 @@
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30438,7 +30438,7 @@
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30542,7 +30542,7 @@
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30594,7 +30594,7 @@
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30646,7 +30646,7 @@
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30698,7 +30698,7 @@
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30802,7 +30802,7 @@
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30906,7 +30906,7 @@
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30958,7 +30958,7 @@
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31010,7 +31010,7 @@
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31062,7 +31062,7 @@
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31166,7 +31166,7 @@
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31218,7 +31218,7 @@
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31270,7 +31270,7 @@
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31322,7 @@
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31374,7 +31374,7 @@
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31426,7 +31426,7 @@
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31530,7 +31530,7 @@
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31582,7 +31582,7 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31634,7 +31634,7 @@
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31686,7 +31686,7 @@
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31842,7 +31842,7 @@
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31894,7 +31894,7 @@
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31946,7 +31946,7 @@
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31998,7 +31998,7 @@
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32154,7 +32154,7 @@
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32206,7 +32206,7 @@
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32258,7 +32258,7 @@
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32310,7 +32310,7 @@
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32414,7 +32414,7 @@
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32518,7 +32518,7 @@
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32570,7 +32570,7 @@
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32622,7 +32622,7 @@
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32674,7 +32674,7 @@
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32778,7 +32778,7 @@
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32830,7 +32830,7 @@
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32882,7 +32882,7 @@
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32986,7 +32986,7 @@
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33038,7 +33038,7 @@
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33142,7 +33142,7 @@
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33194,7 +33194,7 @@
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33246,7 +33246,7 @@
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33298,7 +33298,7 @@
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33454,7 +33454,7 @@
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33506,7 +33506,7 @@
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33558,7 +33558,7 @@
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33662,7 +33662,7 @@
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33714,7 +33714,7 @@
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33766,7 +33766,7 @@
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33870,7 +33870,7 @@
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33922,7 +33922,7 @@
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34026,7 +34026,7 @@
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34078,7 +34078,7 @@
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34130,7 +34130,7 @@
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34182,7 +34182,7 @@
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34234,7 +34234,7 @@
       </c>
       <c r="L650" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34286,7 +34286,7 @@
       </c>
       <c r="L651" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="L652" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34390,7 +34390,7 @@
       </c>
       <c r="L653" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34442,7 +34442,7 @@
       </c>
       <c r="L654" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34494,7 +34494,7 @@
       </c>
       <c r="L655" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34546,7 +34546,7 @@
       </c>
       <c r="L656" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="L657" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -34650,7 +34650,7 @@
       </c>
       <c r="L658" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34702,7 +34702,7 @@
       </c>
       <c r="L659" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34754,7 +34754,7 @@
       </c>
       <c r="L660" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="L661" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34858,7 +34858,7 @@
       </c>
       <c r="L662" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34910,7 +34910,7 @@
       </c>
       <c r="L663" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34962,7 +34962,7 @@
       </c>
       <c r="L664" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-LIMA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LIMA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
